--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/listMemberWorkoutSessions-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/listMemberWorkoutSessions-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
-  <si>
-    <t>Statement: WorkoutSessionService.listMemberWorkoutSessions(memberId, options?) – Always sets memberId in options before calling workoutSessionRepository.findAll({ memberId, ...options }). Supports optional date range and pagination.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="42">
+  <si>
+    <t>Statement: WorkoutSessionService.listMemberWorkoutSessions(id, opts)</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: memberId: string, options?: { startDate?, endDate?, page?, pageSize? }</t>
+    <t>Input: id, opts</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>workoutSessionRepository is accessible</t>
+    <t>repo accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;PageResult&lt;WorkoutSessionWithExercises&gt;&gt;</t>
+    <t>Output: page</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns page of sessions filtered by memberId (plus any additional options).</t>
+    <t>Listed.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,30 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>no extra options</t>
-  </si>
-  <si>
-    <t>passes { memberId } to repo</t>
-  </si>
-  <si>
-    <t>date range opts</t>
-  </si>
-  <si>
-    <t>memberId merged with date range options</t>
-  </si>
-  <si>
-    <t>empty sessions</t>
-  </si>
-  <si>
-    <t>items=[], total=0</t>
-  </si>
-  <si>
-    <t>pagination opts</t>
-  </si>
-  <si>
-    <t>memberId merged with pagination</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -103,100 +79,28 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>memberId="member-001", no options</t>
-  </si>
-  <si>
-    <t>items.length=1; findAll({memberId}) called</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>memberId="member-001", { startDate, endDate, page, pageSize }</t>
-  </si>
-  <si>
-    <t>findAll({ memberId, startDate, endDate, page, pageSize }) called</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>memberId="member-001", no sessions in range</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>memberId="member-001", { page:2, pageSize:5 }</t>
-  </si>
-  <si>
-    <t>findAll({ memberId, page:2, pageSize:5 }) called; total=5</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>empty result</t>
-  </si>
-  <si>
-    <t>No sessions for member → total=0</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>empty</t>
-  </si>
-  <si>
-    <t>memberId with no sessions</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>memberId, no options</t>
-  </si>
-  <si>
-    <t>items.length=1; findAll({memberId})</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>memberId + date range</t>
-  </si>
-  <si>
-    <t>findAll with merged options</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>memberId, empty sessions</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>memberId + pagination</t>
-  </si>
-  <si>
-    <t>findAll with merged pagination</t>
+    <t>List</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -754,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -776,62 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -840,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -852,87 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -943,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -953,24 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -981,7 +750,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -993,36 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1046,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="C1" s="4" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1069,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1089,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,19 +861,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1129,19 +881,199 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1169,16 +1101,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1186,45 +1118,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1233,19 +1165,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/listMemberWorkoutSessions-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/listMemberWorkoutSessions-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="42">
-  <si>
-    <t>Statement: WorkoutSessionService.listMemberWorkoutSessions(id, opts)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="106">
+  <si>
+    <t>Statement: WorkoutSessionService.listMemberWorkoutSessions(memberId, options) – Returns a paginated list of workout sessions for a member. Supports optional filtering by start/end date and pagination. Results may be ordered by date ascending or descending.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: id, opts</t>
+    <t>Input: memberId: string, options?: WorkoutSessionListOptions { startDate?, endDate?, page?, pageSize? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>repo accessible</t>
+    <t>Sessions for the given memberId may or may not exist. All options fields are optional.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: page</t>
+    <t>Output: Promise&lt;PageResult&lt;WorkoutSessionWithExercises&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Listed.</t>
+    <t>On success: PageResult returned with items matching the provided filters and total reflecting the full count.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,54 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Date filter: startDate</t>
+  </si>
+  <si>
+    <t>startDate provided → items[0].date &gt;= startDate</t>
+  </si>
+  <si>
+    <t>Date filter: endDate</t>
+  </si>
+  <si>
+    <t>endDate provided → items[0].date &lt;= endDate</t>
+  </si>
+  <si>
+    <t>Date filter: range</t>
+  </si>
+  <si>
+    <t>startDate + endDate → items[0].date within range</t>
+  </si>
+  <si>
+    <t>Date filters absent</t>
+  </si>
+  <si>
+    <t>No date filters → all sessions returned, items.length: 1, total: 1</t>
+  </si>
+  <si>
+    <t>Pagination</t>
+  </si>
+  <si>
+    <t>page: 2, pageSize: 10 → paginated subset returned, total: 25</t>
+  </si>
+  <si>
+    <t>Data availability</t>
+  </si>
+  <si>
+    <t>No matching sessions → items.length: 0, total: 0</t>
+  </si>
+  <si>
+    <t>Ordering (ASC)</t>
+  </si>
+  <si>
+    <t>Sessions returned in date ascending order → items[0].date &lt; items[1].date</t>
+  </si>
+  <si>
+    <t>Ordering (DESC)</t>
+  </si>
+  <si>
+    <t>Sessions returned in date descending order → items[0].date &gt; items[1].date</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,28 +127,172 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, no options</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0]: MOCK_SESSION_WITH_EXERCISES, total: 1</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, startDate: 2024-06-01</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date &gt;= 2024-06-01</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, endDate: 2024-06-30</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date &lt;= 2024-06-30</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, startDate: 2024-01-01, endDate: 2024-12-31</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date within range</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, page: 2, pageSize: 10</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 25</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>memberId: NONEXISTENT_ID, no options</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 0</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, sessions: [older, newer] (ASC)</t>
+  </si>
+  <si>
+    <t>PageResult with items[0].id: "older", items[1].id: "newer", items[0].date &lt; items[1].date</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, options: { page: 1, pageSize: 10 }, sessions: [newer, older] (DESC)</t>
+  </si>
+  <si>
+    <t>PageResult with items[0].id: "newer", items[1].id: "older", items[0].date &gt; items[1].date</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>Member ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty), 1 char</t>
+  </si>
+  <si>
+    <t>Date range boundary</t>
+  </si>
+  <si>
+    <t>startDate equals endDate (same day)</t>
+  </si>
+  <si>
+    <t>Page number</t>
+  </si>
+  <si>
+    <t>0 (treated as page 1), 1 (first page)</t>
+  </si>
+  <si>
+    <t>Page size</t>
+  </si>
+  <si>
+    <t>1 (one item per page)</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>memberId: "", no options</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>memberId: "a", no options</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].memberId: MEMBER_ID</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, startDate: 2024-06-01, endDate: 2024-06-01</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date: 2024-06-01</t>
+  </si>
+  <si>
+    <t>BVA-3 (p=0)</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, page: 0</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, total: 5 (first page)</t>
+  </si>
+  <si>
+    <t>BVA-3 (p=1)</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, page: 1</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, pageSize: 1</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, total: 5</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>List</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -133,7 +325,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-05</t>
+    <t>SERV-24</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +872,118 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +992,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +1004,155 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +1173,57 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +1246,121 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -785,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -798,22 +1384,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +1407,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1427,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1447,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1467,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,19 +1487,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,19 +1507,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -941,19 +1527,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -961,19 +1547,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,19 +1567,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,19 +1587,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,19 +1607,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,19 +1627,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1061,19 +1647,39 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1101,16 +1707,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1118,45 +1724,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="B3" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1165,19 +1771,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/listMemberWorkoutSessions-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/listMemberWorkoutSessions-bbt-form.xlsx
@@ -325,7 +325,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-24</t>
+    <t>SERV-25</t>
   </si>
   <si>
     <t>n/a</t>
